--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487072_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487072_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8509</v>
+        <v>4.3586</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2307</v>
+        <v>1.6313</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6202</v>
+        <v>2.7273</v>
       </c>
       <c r="G2" t="n">
         <v>3.1106</v>
@@ -610,13 +610,13 @@
         <v>2.5091</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8038</v>
+        <v>-0.2961</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7139</v>
+        <v>-0.3133</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.08989999999999999</v>
+        <v>0.0172</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6932</v>
+        <v>4.1533</v>
       </c>
       <c r="E3" t="n">
-        <v>2.731</v>
+        <v>3.191</v>
       </c>
       <c r="F3" t="n">
         <v>0.9623</v>
@@ -688,10 +688,10 @@
         <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3107</v>
+        <v>0.1494</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4164</v>
+        <v>0.0436</v>
       </c>
       <c r="U3" t="n">
         <v>0.1057</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5561</v>
+        <v>4.0102</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7197</v>
+        <v>2.8793</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8365</v>
+        <v>1.1309</v>
       </c>
       <c r="G4" t="n">
         <v>1.2451</v>
@@ -766,13 +766,13 @@
         <v>1.7371</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3682</v>
+        <v>0.0859</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0462</v>
+        <v>0.1134</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3219</v>
+        <v>-0.0275</v>
       </c>
       <c r="V4" t="n">
         <v>0.9421</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2185</v>
+        <v>2.5641</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4596</v>
+        <v>1.6178</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7589</v>
+        <v>0.9463</v>
       </c>
       <c r="G5" t="n">
         <v>1.1605</v>
@@ -844,13 +844,13 @@
         <v>2.3161</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4211</v>
+        <v>-0.2333</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9915</v>
+        <v>0.1497</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5705</v>
+        <v>-0.3831</v>
       </c>
       <c r="V5" t="n">
         <v>0.2859</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.445</v>
+        <v>1.2834</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0946</v>
+        <v>0.2542</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3504</v>
+        <v>1.0292</v>
       </c>
       <c r="G6" t="n">
         <v>4.7551</v>
@@ -922,13 +922,13 @@
         <v>1.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1521</v>
+        <v>-0.3137</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4032</v>
+        <v>-0.2435</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2511</v>
+        <v>-0.0701</v>
       </c>
       <c r="V6" t="n">
         <v>-1.228</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. HERNANDO PEREZ</t>
+          <t>B. DE LA LLAMA RUIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7346</v>
+        <v>0.5041</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8114</v>
+        <v>0.4816</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.0225</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9754</v>
+        <v>-0.203</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3203</v>
+        <v>1.7719</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3449</v>
+        <v>-1.975</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4554</v>
+        <v>-0.0164</v>
       </c>
       <c r="K7" t="n">
-        <v>3.374</v>
+        <v>1.9457</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0814</v>
+        <v>-1.9621</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.48</v>
+        <v>-0.1866</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0537</v>
+        <v>-0.1738</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4263</v>
+        <v>-0.0129</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.3161</v>
+        <v>0.386</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.579</v>
+        <v>0.386</v>
       </c>
       <c r="S7" t="n">
-        <v>0.07530000000000001</v>
+        <v>-0.2928</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2512</v>
+        <v>-0.116</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1759</v>
+        <v>-0.1768</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. REINER</t>
+          <t>M. HERNANDO PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4774</v>
+        <v>0.4342</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7101</v>
+        <v>0.511</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1875</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9735</v>
+        <v>2.9754</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7518</v>
+        <v>3.3203</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7783</v>
+        <v>-0.3449</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7392</v>
+        <v>3.4554</v>
       </c>
       <c r="K8" t="n">
-        <v>4.0259</v>
+        <v>3.374</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2866</v>
+        <v>0.0814</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2343</v>
+        <v>-0.48</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2741</v>
+        <v>-0.0537</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5084</v>
+        <v>-0.4263</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.7371</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.8602</v>
+        <v>-2.8951</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1231</v>
+        <v>0.579</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3887</v>
+        <v>-0.2251</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8328</v>
+        <v>-0.0492</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4441</v>
+        <v>-0.1759</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3704</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2436</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GOMEZ FERNANDEZ</t>
+          <t>J. REINER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1712</v>
+        <v>0.3485</v>
       </c>
       <c r="E9" t="n">
-        <v>0.427</v>
+        <v>-1.2501</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2559</v>
+        <v>1.5986</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5169</v>
+        <v>2.9735</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1635</v>
+        <v>3.7518</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6805</v>
+        <v>-0.7783</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6107</v>
+        <v>2.7392</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0569</v>
+        <v>4.0259</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6676</v>
+        <v>-1.2866</v>
       </c>
       <c r="M9" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.2343</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1067</v>
+        <v>-0.2741</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0129</v>
+        <v>0.5084</v>
       </c>
       <c r="P9" t="n">
-        <v>0.193</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.8602</v>
       </c>
       <c r="R9" t="n">
-        <v>0.193</v>
+        <v>2.1231</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4951</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0378</v>
+        <v>-0.3728</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5427</v>
+        <v>-0.1448</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.3704</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2436</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. DE LA LLAMA RUIZ</t>
+          <t>A. GOMEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1234</v>
+        <v>-0.3424</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1812</v>
+        <v>-0.274</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0578</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.203</v>
+        <v>-0.5169</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7719</v>
+        <v>0.1635</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.975</v>
+        <v>-0.6805</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0164</v>
+        <v>-0.6107</v>
       </c>
       <c r="K10" t="n">
-        <v>1.9457</v>
+        <v>0.0569</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9621</v>
+        <v>-0.6676</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1866</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1738</v>
+        <v>0.1067</v>
       </c>
       <c r="O10" t="n">
         <v>-0.0129</v>
       </c>
       <c r="P10" t="n">
-        <v>0.386</v>
+        <v>0.193</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.386</v>
+        <v>0.193</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6736</v>
+        <v>-0.0185</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4164</v>
+        <v>0.3368</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2571</v>
+        <v>-0.3553</v>
       </c>
       <c r="V10" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8846</v>
+        <v>-2.6308</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2618</v>
+        <v>-1.0615</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6228</v>
+        <v>-1.5693</v>
       </c>
       <c r="G11" t="n">
         <v>0.9574</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.661</v>
+        <v>-0.4072</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3569</v>
+        <v>-0.1566</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3041</v>
+        <v>-0.2505</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2859</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.3857</v>
+        <v>14.6832</v>
       </c>
       <c r="E12" t="n">
-        <v>7.683299999999998</v>
+        <v>7.980600000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>6.702500000000001</v>
+        <v>6.702499999999999</v>
       </c>
       <c r="G12" t="n">
         <v>20.6317</v>
@@ -1375,7 +1375,7 @@
         <v>-1.4616</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5367000000000001</v>
+        <v>-0.5367000000000002</v>
       </c>
       <c r="O12" t="n">
         <v>-0.9248000000000001</v>
@@ -1390,13 +1390,13 @@
         <v>13.5106</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3666</v>
+        <v>-2.069</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9053</v>
+        <v>-0.6079000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.4612</v>
+        <v>-1.4611</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9843999999999999</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>C. POLANCO MERINO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6677</v>
+        <v>1.588</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1144</v>
+        <v>0.8126</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4467</v>
+        <v>0.7754</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.1313</v>
+        <v>0.4636</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1106</v>
+        <v>-0.9801</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0207</v>
+        <v>1.4438</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7334</v>
+        <v>0.9372</v>
       </c>
       <c r="K13" t="n">
-        <v>1.4485</v>
+        <v>-0.2588</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2849</v>
+        <v>1.196</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.8647</v>
+        <v>-0.4735</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.5591</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3056</v>
+        <v>0.2478</v>
       </c>
       <c r="P13" t="n">
-        <v>0.193</v>
+        <v>1.158</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.0881</v>
+        <v>1.158</v>
       </c>
       <c r="S13" t="n">
-        <v>4.0922</v>
+        <v>-0.3196</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9626</v>
+        <v>-0.4104</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1296</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5138</v>
+        <v>0.2859</v>
       </c>
       <c r="W13" t="n">
-        <v>3.3135</v>
+        <v>0.2859</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. SAN JOSE GONZALEZ</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7784</v>
+        <v>1.0026</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6759</v>
+        <v>3.0115</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8976</v>
+        <v>-2.0089</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4544</v>
+        <v>-2.1313</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5536</v>
+        <v>-2.1106</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0993</v>
+        <v>-0.0207</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0083</v>
+        <v>1.7334</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9676</v>
+        <v>1.4485</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0407</v>
+        <v>0.2849</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-3.8647</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.414</v>
+        <v>-3.5591</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.14</v>
+        <v>-0.3056</v>
       </c>
       <c r="P14" t="n">
-        <v>0.386</v>
+        <v>0.193</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R14" t="n">
-        <v>0.386</v>
+        <v>3.0881</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5518999999999999</v>
+        <v>1.4271</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6676</v>
+        <v>0.8597</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1157</v>
+        <v>0.5674</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.614</v>
+        <v>1.5138</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.3135</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.614</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. POLANCO MERINO</t>
+          <t>J. SAN JOSE GONZALEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7462</v>
+        <v>0.5047</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2117</v>
+        <v>1.3755</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5345</v>
+        <v>-0.8708</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4636</v>
+        <v>0.4544</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9801</v>
+        <v>0.5536</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4438</v>
+        <v>-0.0993</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9372</v>
+        <v>1.0083</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2588</v>
+        <v>0.9676</v>
       </c>
       <c r="L15" t="n">
-        <v>1.196</v>
+        <v>0.0407</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4735</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.414</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2478</v>
+        <v>-0.14</v>
       </c>
       <c r="P15" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1614</v>
+        <v>0.2783</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0113</v>
+        <v>0.3672</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1501</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2859</v>
+        <v>-0.614</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2467</v>
+        <v>0.2606</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0505</v>
+        <v>-0.2508</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2972</v>
+        <v>0.5114</v>
       </c>
       <c r="G16" t="n">
         <v>-1.4841</v>
@@ -1702,13 +1702,13 @@
         <v>2.1231</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2446</v>
+        <v>0.2585</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5764</v>
+        <v>0.3761</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3318</v>
+        <v>-0.1177</v>
       </c>
       <c r="V16" t="n">
         <v>0.3281</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2755</v>
+        <v>-0.1149</v>
       </c>
       <c r="E17" t="n">
         <v>-0.4858</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2103</v>
+        <v>0.3709</v>
       </c>
       <c r="G17" t="n">
         <v>-1.3913</v>
@@ -1780,13 +1780,13 @@
         <v>1.158</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0423</v>
+        <v>0.1183</v>
       </c>
       <c r="T17" t="n">
         <v>0.2512</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2935</v>
+        <v>-0.1329</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6293</v>
+        <v>-0.4558</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1248</v>
+        <v>0.3251</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7541</v>
+        <v>-0.7809</v>
       </c>
       <c r="G18" t="n">
         <v>-1.7434</v>
@@ -1858,13 +1858,13 @@
         <v>0.965</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1368</v>
+        <v>0.0367</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1057</v>
+        <v>0.0945</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0311</v>
+        <v>-0.0579</v>
       </c>
       <c r="V18" t="n">
         <v>0.2859</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8622</v>
+        <v>-0.8424</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7452</v>
+        <v>-0.645</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.117</v>
+        <v>-0.1973</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1801</v>
@@ -1936,13 +1936,13 @@
         <v>0.193</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1249</v>
+        <v>0.1448</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.119</v>
+        <v>-0.0188</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2439</v>
+        <v>0.1636</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. JIMENEZ EL MERZOUG</t>
+          <t>R. GONZALEZ RUIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2731</v>
+        <v>-1.7293</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4898</v>
+        <v>-0.5777</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7833</v>
+        <v>-1.1516</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.5232</v>
+        <v>-2.2809</v>
       </c>
       <c r="H20" t="n">
-        <v>-4.5893</v>
+        <v>-2.7871</v>
       </c>
       <c r="I20" t="n">
-        <v>1.066</v>
+        <v>0.5062</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1613</v>
+        <v>0.7832</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.6045</v>
+        <v>0.1242</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7658</v>
+        <v>0.6591</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.6845</v>
+        <v>-3.0641</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.9848</v>
+        <v>-2.9113</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6998</v>
+        <v>-0.1528</v>
       </c>
       <c r="P20" t="n">
-        <v>0.579</v>
+        <v>1.158</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5091</v>
+        <v>2.1231</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3008</v>
+        <v>-0.3206</v>
       </c>
       <c r="T20" t="n">
-        <v>0.279</v>
+        <v>-0.3959</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0218</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3704</v>
+        <v>-0.2859</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3704</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. GONZALEZ RUIZ</t>
+          <t>I. JIMENEZ EL MERZOUG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4372</v>
+        <v>-1.9856</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1785</v>
+        <v>-1.3897</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2586</v>
+        <v>-0.5959</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2809</v>
+        <v>-3.5232</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.7871</v>
+        <v>-4.5893</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5062</v>
+        <v>1.066</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7832</v>
+        <v>0.1613</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1242</v>
+        <v>-1.6045</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6591</v>
+        <v>1.7658</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.0641</v>
+        <v>-3.6845</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.9113</v>
+        <v>-2.9848</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1528</v>
+        <v>-0.6998</v>
       </c>
       <c r="P21" t="n">
-        <v>1.158</v>
+        <v>0.579</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1231</v>
+        <v>2.5091</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0285</v>
+        <v>0.5883</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9967</v>
+        <v>0.3791</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0317</v>
+        <v>0.2092</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2859</v>
+        <v>0.3704</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2859</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.8783</v>
+        <v>-4.9503</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.6165</v>
+        <v>-3.7152</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2618</v>
+        <v>-1.2351</v>
       </c>
       <c r="G22" t="n">
         <v>-4.6191</v>
@@ -2170,13 +2170,13 @@
         <v>1.5441</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8732</v>
+        <v>0.0549</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8778</v>
+        <v>0.0235</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0046</v>
+        <v>0.0314</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.4691</v>
+        <v>-7.6634</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2631</v>
+        <v>-5.1629</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.206</v>
+        <v>-2.5005</v>
       </c>
       <c r="G23" t="n">
         <v>-3.1962</v>
@@ -2248,13 +2248,13 @@
         <v>1.158</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2941</v>
+        <v>0.0998</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1652</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4594</v>
+        <v>0.1649</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8999</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-14.3857</v>
+        <v>-14.3858</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.7026</v>
+        <v>-6.7024</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.6831</v>
+        <v>-7.683300000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-20.6316</v>
@@ -2305,7 +2305,7 @@
         <v>0.5369999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9248999999999996</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-22.0932</v>
@@ -2317,7 +2317,7 @@
         <v>-2.2281</v>
       </c>
       <c r="P24" t="n">
-        <v>2.894799999999999</v>
+        <v>2.8948</v>
       </c>
       <c r="Q24" t="n">
         <v>-13.5105</v>
@@ -2326,13 +2326,13 @@
         <v>16.4055</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3663</v>
+        <v>2.3665</v>
       </c>
       <c r="T24" t="n">
         <v>1.4611</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9054</v>
+        <v>0.9053</v>
       </c>
       <c r="V24" t="n">
         <v>0.9843000000000001</v>
